--- a/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/03_PCB_MAIN_заказ_с_DFM/01_Изготовление_платы/PCB-MAIN_ИМПЕДАНС_ТРАССЫ_REV_D.xlsx
+++ b/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/03_PCB_MAIN_заказ_с_DFM/01_Изготовление_платы/PCB-MAIN_ИМПЕДАНС_ТРАССЫ_REV_D.xlsx
@@ -457,7 +457,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PCB-MAIN Rev B. Фактические дорожки / As-routed traces. Цели завода ожидают решения / Factory targets pending.</t>
+          <t>PCB-MAIN Rev B. Фактические дорожки / As-routed traces. EVT: no controlled-impedance target ordered.</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -549,7 +549,7 @@
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>PENDING_CUSTOMER_DECISION_AND_SELECTED_STACK</t>
+          <t>EVT_AS_ROUTED_NO_CONTROLLED_IMPEDANCE_ORDERED</t>
         </is>
       </c>
     </row>
